--- a/data/course_data_B24.xlsx
+++ b/data/course_data_B24.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ercx2\Desktop\Scheduling Theory_02\Paper\scheduling\Campus-Scheduling\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ercx2\Desktop\Scheduling\Campus-Scheduling\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10656E90-4A94-4C86-86A2-83F8E78E7352}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1CDD87E-985A-4946-AF77-2DF4807EC20B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="5940" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1482,20 +1482,9 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4D257DAD-E412-40CE-835B-244614789DDA}" name="Table1" displayName="Table1" ref="A1:H227" totalsRowShown="0" headerRowDxfId="11" dataDxfId="9" headerRowBorderDxfId="10" tableBorderDxfId="8">
-  <autoFilter ref="A1:H227" xr:uid="{4D257DAD-E412-40CE-835B-244614789DDA}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Elektrik-Elektronik Mühendisliği"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="3">
-      <filters>
-        <filter val="4"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H227">
-    <sortCondition descending="1" ref="G1:G227"/>
+  <autoFilter ref="A1:H227" xr:uid="{4D257DAD-E412-40CE-835B-244614789DDA}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:H193">
+    <sortCondition ref="D1:D227"/>
   </sortState>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{E28ED7F9-92E9-43FB-898A-30B6DDD841D3}" name="DepartmentName" dataDxfId="7"/>
@@ -1833,7 +1822,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>21</v>
       </c>
@@ -1859,7 +1848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>21</v>
       </c>
@@ -1885,7 +1874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>21</v>
       </c>
@@ -1911,7 +1900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>21</v>
       </c>
@@ -1937,7 +1926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>24</v>
       </c>
@@ -1963,59 +1952,59 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>122</v>
+        <v>50</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>123</v>
+        <v>51</v>
       </c>
       <c r="D7" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F7" s="2">
-        <v>7208507</v>
+        <v>1635809</v>
       </c>
       <c r="G7" s="2">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="H7" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>22</v>
+        <v>325</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>23</v>
+        <v>327</v>
       </c>
       <c r="D8" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F8" s="2">
-        <v>2117533</v>
+        <v>5320332</v>
       </c>
       <c r="G8" s="2">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="H8" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>24</v>
       </c>
@@ -2041,7 +2030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
@@ -2067,15 +2056,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D11" s="2">
         <v>2</v>
@@ -2084,16 +2073,16 @@
         <v>13</v>
       </c>
       <c r="F11" s="2">
-        <v>2923606</v>
+        <v>7208507</v>
       </c>
       <c r="G11" s="2">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="H11" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>24</v>
       </c>
@@ -2119,33 +2108,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="D13" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F13" s="2">
-        <v>1635809</v>
+        <v>2117533</v>
       </c>
       <c r="G13" s="2">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="H13" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>7</v>
       </c>
@@ -2171,33 +2160,33 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>325</v>
+        <v>126</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>327</v>
+        <v>127</v>
       </c>
       <c r="D15" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F15" s="2">
-        <v>5320332</v>
+        <v>2923606</v>
       </c>
       <c r="G15" s="2">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="H15" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>7</v>
       </c>
@@ -2223,33 +2212,33 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>314</v>
+        <v>130</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>315</v>
+        <v>131</v>
       </c>
       <c r="D17" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F17" s="2">
-        <v>4721220</v>
+        <v>1540100</v>
       </c>
       <c r="G17" s="2">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="H17" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>24</v>
       </c>
@@ -2275,15 +2264,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>130</v>
+        <v>109</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>131</v>
+        <v>110</v>
       </c>
       <c r="D19" s="2">
         <v>2</v>
@@ -2292,50 +2281,50 @@
         <v>10</v>
       </c>
       <c r="F19" s="2">
-        <v>1540100</v>
+        <v>2148154</v>
       </c>
       <c r="G19" s="2">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="H19" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>259</v>
+        <v>90</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>260</v>
+        <v>91</v>
       </c>
       <c r="D20" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F20" s="2">
-        <v>4693090</v>
+        <v>9931948</v>
       </c>
       <c r="G20" s="2">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H20" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>90</v>
+        <v>322</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>91</v>
+        <v>323</v>
       </c>
       <c r="D21" s="2">
         <v>1</v>
@@ -2344,128 +2333,128 @@
         <v>10</v>
       </c>
       <c r="F21" s="2">
-        <v>9931948</v>
+        <v>5320332</v>
       </c>
       <c r="G21" s="2">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="H21" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>398</v>
+        <v>162</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>399</v>
+        <v>161</v>
       </c>
       <c r="D22" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F22" s="2">
-        <v>2994200</v>
+        <v>2132049</v>
       </c>
       <c r="G22" s="2">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="H22" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>420</v>
+        <v>232</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>421</v>
+        <v>233</v>
       </c>
       <c r="D23" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F23" s="2">
-        <v>1021641</v>
+        <v>2977082</v>
       </c>
       <c r="G23" s="2">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="H23" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D24" s="2">
         <v>2</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F24" s="2">
         <v>2148154</v>
       </c>
       <c r="G24" s="2">
-        <v>129</v>
+        <v>82</v>
       </c>
       <c r="H24" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>330</v>
+        <v>78</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>331</v>
+        <v>79</v>
       </c>
       <c r="D25" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F25" s="2">
-        <v>1029126</v>
+        <v>3261519</v>
       </c>
       <c r="G25" s="2">
-        <v>128</v>
+        <v>68</v>
       </c>
       <c r="H25" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>322</v>
+        <v>251</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>323</v>
+        <v>252</v>
       </c>
       <c r="D26" s="2">
         <v>1</v>
@@ -2474,76 +2463,76 @@
         <v>10</v>
       </c>
       <c r="F26" s="2">
-        <v>5320332</v>
+        <v>1267061</v>
       </c>
       <c r="G26" s="2">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="H26" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>422</v>
+        <v>263</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>423</v>
+        <v>264</v>
       </c>
       <c r="D27" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F27" s="2">
-        <v>2092090</v>
+        <v>1041914</v>
       </c>
       <c r="G27" s="2">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="H27" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>15</v>
+        <v>274</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>16</v>
+        <v>275</v>
       </c>
       <c r="D28" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F28" s="2">
-        <v>3048102</v>
+        <v>2550816</v>
       </c>
       <c r="G28" s="2">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="H28" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>146</v>
+        <v>314</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>147</v>
+        <v>315</v>
       </c>
       <c r="D29" s="2">
         <v>3</v>
@@ -2552,24 +2541,24 @@
         <v>10</v>
       </c>
       <c r="F29" s="2">
-        <v>3218866</v>
+        <v>4721220</v>
       </c>
       <c r="G29" s="2">
-        <v>124</v>
+        <v>144</v>
       </c>
       <c r="H29" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>162</v>
+        <v>60</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>161</v>
+        <v>59</v>
       </c>
       <c r="D30" s="2">
         <v>1</v>
@@ -2578,50 +2567,50 @@
         <v>10</v>
       </c>
       <c r="F30" s="2">
-        <v>2132049</v>
+        <v>1307360</v>
       </c>
       <c r="G30" s="2">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="H30" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>84</v>
+        <v>325</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>85</v>
+        <v>326</v>
       </c>
       <c r="D31" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F31" s="2">
-        <v>2238227</v>
+        <v>5320332</v>
       </c>
       <c r="G31" s="2">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="H31" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>232</v>
+        <v>370</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>233</v>
+        <v>371</v>
       </c>
       <c r="D32" s="2">
         <v>1</v>
@@ -2630,16 +2619,16 @@
         <v>10</v>
       </c>
       <c r="F32" s="2">
-        <v>2977082</v>
+        <v>1214802</v>
       </c>
       <c r="G32" s="2">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="H32" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
         <v>19</v>
       </c>
@@ -2665,41 +2654,41 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>272</v>
+        <v>398</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>273</v>
+        <v>399</v>
       </c>
       <c r="D34" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F34" s="2">
-        <v>2579557</v>
+        <v>2994200</v>
       </c>
       <c r="G34" s="2">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="H34" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>251</v>
+        <v>148</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>252</v>
+        <v>149</v>
       </c>
       <c r="D35" s="2">
         <v>1</v>
@@ -2708,50 +2697,50 @@
         <v>10</v>
       </c>
       <c r="F35" s="2">
-        <v>1267061</v>
+        <v>9931948</v>
       </c>
       <c r="G35" s="2">
-        <v>115</v>
+        <v>13</v>
       </c>
       <c r="H35" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>60</v>
+        <v>301</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>59</v>
+        <v>302</v>
       </c>
       <c r="D36" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F36" s="2">
-        <v>1307360</v>
+        <v>1235319</v>
       </c>
       <c r="G36" s="2">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="H36" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>263</v>
+        <v>158</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>264</v>
+        <v>159</v>
       </c>
       <c r="D37" s="2">
         <v>1</v>
@@ -2760,50 +2749,50 @@
         <v>10</v>
       </c>
       <c r="F37" s="2">
-        <v>1041914</v>
+        <v>1385355</v>
       </c>
       <c r="G37" s="2">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="H37" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>119</v>
+        <v>58</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>120</v>
+        <v>59</v>
       </c>
       <c r="D38" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F38" s="2">
-        <v>4270666</v>
+        <v>1684669</v>
       </c>
       <c r="G38" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="H38" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>220</v>
+        <v>330</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>221</v>
+        <v>331</v>
       </c>
       <c r="D39" s="2">
         <v>3</v>
@@ -2812,128 +2801,128 @@
         <v>13</v>
       </c>
       <c r="F39" s="2">
-        <v>3041802</v>
+        <v>1029126</v>
       </c>
       <c r="G39" s="2">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="H39" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>400</v>
+        <v>251</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>401</v>
+        <v>252</v>
       </c>
       <c r="D40" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F40" s="2">
-        <v>2458943</v>
+        <v>3074554</v>
       </c>
       <c r="G40" s="2">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="H40" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>44</v>
+        <v>420</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>45</v>
+        <v>421</v>
       </c>
       <c r="D41" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F41" s="2">
-        <v>2669297</v>
+        <v>1021641</v>
       </c>
       <c r="G41" s="2">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="H41" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>362</v>
+        <v>259</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>363</v>
+        <v>260</v>
       </c>
       <c r="D42" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F42" s="2">
-        <v>1267061</v>
+        <v>4693090</v>
       </c>
       <c r="G42" s="2">
-        <v>102</v>
+        <v>135</v>
       </c>
       <c r="H42" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>274</v>
+        <v>422</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>275</v>
+        <v>423</v>
       </c>
       <c r="D43" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F43" s="2">
-        <v>2550816</v>
+        <v>2092090</v>
       </c>
       <c r="G43" s="2">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="H43" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
       <c r="D44" s="2">
         <v>2</v>
@@ -2942,50 +2931,50 @@
         <v>10</v>
       </c>
       <c r="F44" s="2">
-        <v>2903204</v>
+        <v>2238227</v>
       </c>
       <c r="G44" s="2">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="H44" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>226</v>
+        <v>299</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>227</v>
+        <v>300</v>
       </c>
       <c r="D45" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F45" s="2">
-        <v>2576518</v>
+        <v>1618088</v>
       </c>
       <c r="G45" s="2">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H45" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D46" s="2">
         <v>2</v>
@@ -2994,24 +2983,24 @@
         <v>10</v>
       </c>
       <c r="F46" s="2">
-        <v>1235319</v>
+        <v>2832797</v>
       </c>
       <c r="G46" s="2">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H46" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>299</v>
+        <v>113</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>300</v>
+        <v>114</v>
       </c>
       <c r="D47" s="2">
         <v>2</v>
@@ -3023,39 +3012,39 @@
         <v>1618088</v>
       </c>
       <c r="G47" s="2">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="H47" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>230</v>
+        <v>132</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>231</v>
+        <v>133</v>
       </c>
       <c r="D48" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F48" s="2">
-        <v>3952988</v>
+        <v>1600939</v>
       </c>
       <c r="G48" s="2">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="H48" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
         <v>19</v>
       </c>
@@ -3081,7 +3070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
         <v>19</v>
       </c>
@@ -3107,93 +3096,93 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>370</v>
+        <v>15</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>371</v>
+        <v>16</v>
       </c>
       <c r="D51" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F51" s="2">
-        <v>1214802</v>
+        <v>3048102</v>
       </c>
       <c r="G51" s="2">
-        <v>97</v>
+        <v>125</v>
       </c>
       <c r="H51" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="D52" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F52" s="2">
-        <v>1318658</v>
+        <v>4270666</v>
       </c>
       <c r="G52" s="2">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="H52" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>303</v>
+        <v>272</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>304</v>
+        <v>273</v>
       </c>
       <c r="D53" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F53" s="2">
-        <v>2832797</v>
+        <v>2579557</v>
       </c>
       <c r="G53" s="2">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="H53" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="D54" s="2">
         <v>2</v>
@@ -3202,154 +3191,154 @@
         <v>10</v>
       </c>
       <c r="F54" s="2">
-        <v>9931948</v>
+        <v>2903204</v>
       </c>
       <c r="G54" s="2">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="H54" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="D55" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F55" s="2">
-        <v>2571190</v>
+        <v>1047857</v>
       </c>
       <c r="G55" s="2">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="H55" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>113</v>
+        <v>226</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>114</v>
+        <v>227</v>
       </c>
       <c r="D56" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F56" s="2">
-        <v>1618088</v>
+        <v>2576518</v>
       </c>
       <c r="G56" s="2">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="H56" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>325</v>
+        <v>101</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>326</v>
+        <v>102</v>
       </c>
       <c r="D57" s="2">
+        <v>2</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F57" s="2">
+        <v>9931948</v>
+      </c>
+      <c r="G57" s="2">
+        <v>96</v>
+      </c>
+      <c r="H57" s="2">
         <v>1</v>
       </c>
-      <c r="E57" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F57" s="2">
-        <v>5320332</v>
-      </c>
-      <c r="G57" s="2">
-        <v>95</v>
-      </c>
-      <c r="H57" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>158</v>
+        <v>400</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>159</v>
+        <v>401</v>
       </c>
       <c r="D58" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F58" s="2">
-        <v>1385355</v>
+        <v>2458943</v>
       </c>
       <c r="G58" s="2">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="H58" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>397</v>
+        <v>62</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>396</v>
+        <v>63</v>
       </c>
       <c r="D59" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F59" s="2">
-        <v>5856415</v>
+        <v>1457877</v>
       </c>
       <c r="G59" s="2">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="H59" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>389</v>
+        <v>251</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>390</v>
+        <v>252</v>
       </c>
       <c r="D60" s="2">
         <v>1</v>
@@ -3358,50 +3347,50 @@
         <v>10</v>
       </c>
       <c r="F60" s="2">
-        <v>1047857</v>
+        <v>2571190</v>
       </c>
       <c r="G60" s="2">
-        <v>90</v>
+        <v>54</v>
       </c>
       <c r="H60" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>210</v>
+        <v>8</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>211</v>
+        <v>9</v>
       </c>
       <c r="D61" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F61" s="2">
-        <v>3143825</v>
+        <v>3435711</v>
       </c>
       <c r="G61" s="2">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="H61" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="D62" s="2">
         <v>3</v>
@@ -3410,50 +3399,50 @@
         <v>10</v>
       </c>
       <c r="F62" s="2">
-        <v>3143825</v>
+        <v>1267061</v>
       </c>
       <c r="G62" s="2">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="H62" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>342</v>
+        <v>397</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>343</v>
+        <v>396</v>
       </c>
       <c r="D63" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F63" s="2">
-        <v>2137934</v>
+        <v>5856415</v>
       </c>
       <c r="G63" s="2">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="H63" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>201</v>
+        <v>231</v>
       </c>
       <c r="D64" s="2">
         <v>3</v>
@@ -3462,10 +3451,10 @@
         <v>10</v>
       </c>
       <c r="F64" s="2">
-        <v>5299061</v>
+        <v>3952988</v>
       </c>
       <c r="G64" s="2">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="H64" s="2">
         <v>0</v>
@@ -3476,54 +3465,54 @@
         <v>21</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>191</v>
+        <v>146</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>190</v>
+        <v>147</v>
       </c>
       <c r="D65" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F65" s="2">
-        <v>3369135</v>
+        <v>3218866</v>
       </c>
       <c r="G65" s="2">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="H65" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>111</v>
+        <v>220</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>112</v>
+        <v>221</v>
       </c>
       <c r="D66" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F66" s="2">
-        <v>2148154</v>
+        <v>3041802</v>
       </c>
       <c r="G66" s="2">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="H66" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
         <v>19</v>
       </c>
@@ -3549,7 +3538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
         <v>14</v>
       </c>
@@ -3575,59 +3564,59 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>132</v>
+        <v>200</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>133</v>
+        <v>201</v>
       </c>
       <c r="D69" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F69" s="2">
-        <v>1600939</v>
+        <v>5299061</v>
       </c>
       <c r="G69" s="2">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H69" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>121</v>
+        <v>20</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>120</v>
+        <v>16</v>
       </c>
       <c r="D70" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F70" s="2">
-        <v>5293627</v>
+        <v>2061533</v>
       </c>
       <c r="G70" s="2">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="H70" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A71" s="2" t="s">
         <v>21</v>
       </c>
@@ -3653,7 +3642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
         <v>21</v>
       </c>
@@ -3679,7 +3668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A73" s="2" t="s">
         <v>14</v>
       </c>
@@ -3705,59 +3694,59 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>228</v>
+        <v>210</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="D74" s="2">
         <v>3</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F74" s="2">
-        <v>1842843</v>
+        <v>3143825</v>
       </c>
       <c r="G74" s="2">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="H74" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="D75" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F75" s="2">
-        <v>1684669</v>
+        <v>2669297</v>
       </c>
       <c r="G75" s="2">
-        <v>74</v>
+        <v>105</v>
       </c>
       <c r="H75" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
         <v>24</v>
       </c>
@@ -3783,7 +3772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
         <v>21</v>
       </c>
@@ -3809,41 +3798,41 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="D78" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F78" s="2">
-        <v>2137934</v>
+        <v>1767743</v>
       </c>
       <c r="G78" s="2">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H78" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>391</v>
+        <v>95</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>392</v>
+        <v>96</v>
       </c>
       <c r="D79" s="2">
         <v>3</v>
@@ -3852,24 +3841,24 @@
         <v>10</v>
       </c>
       <c r="F79" s="2">
-        <v>1583231</v>
+        <v>1318658</v>
       </c>
       <c r="G79" s="2">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="H79" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>377</v>
+        <v>391</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>378</v>
+        <v>392</v>
       </c>
       <c r="D80" s="2">
         <v>3</v>
@@ -3878,7 +3867,7 @@
         <v>10</v>
       </c>
       <c r="F80" s="2">
-        <v>1198965</v>
+        <v>1583231</v>
       </c>
       <c r="G80" s="2">
         <v>73</v>
@@ -3887,24 +3876,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>251</v>
+        <v>377</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>252</v>
+        <v>378</v>
       </c>
       <c r="D81" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F81" s="2">
-        <v>3074554</v>
+        <v>1198965</v>
       </c>
       <c r="G81" s="2">
         <v>73</v>
@@ -3913,15 +3902,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>20</v>
+        <v>183</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>16</v>
+        <v>184</v>
       </c>
       <c r="D82" s="2">
         <v>2</v>
@@ -3930,24 +3919,24 @@
         <v>10</v>
       </c>
       <c r="F82" s="2">
-        <v>2061533</v>
+        <v>1740446</v>
       </c>
       <c r="G82" s="2">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="H82" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>82</v>
+        <v>358</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>83</v>
+        <v>359</v>
       </c>
       <c r="D83" s="2">
         <v>3</v>
@@ -3956,16 +3945,16 @@
         <v>10</v>
       </c>
       <c r="F83" s="2">
-        <v>3013005</v>
+        <v>3143825</v>
       </c>
       <c r="G83" s="2">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="H83" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
         <v>21</v>
       </c>
@@ -3991,7 +3980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A85" s="2" t="s">
         <v>21</v>
       </c>
@@ -4017,41 +4006,41 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="D86" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F86" s="2">
-        <v>1457877</v>
+        <v>4392170</v>
       </c>
       <c r="G86" s="2">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="H86" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="D87" s="2">
         <v>2</v>
@@ -4060,16 +4049,16 @@
         <v>10</v>
       </c>
       <c r="F87" s="2">
-        <v>1767743</v>
+        <v>1494406</v>
       </c>
       <c r="G87" s="2">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="H87" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
         <v>14</v>
       </c>
@@ -4095,7 +4084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
         <v>14</v>
       </c>
@@ -4121,105 +4110,105 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>78</v>
+        <v>287</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>79</v>
+        <v>288</v>
       </c>
       <c r="D90" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F90" s="2">
-        <v>3261519</v>
+        <v>1121323</v>
       </c>
       <c r="G90" s="2">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="H90" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>183</v>
+        <v>234</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>184</v>
+        <v>235</v>
       </c>
       <c r="D91" s="2">
         <v>2</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F91" s="2">
-        <v>1740446</v>
+        <v>3258742</v>
       </c>
       <c r="G91" s="2">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="H91" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>8</v>
+        <v>228</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>9</v>
+        <v>229</v>
       </c>
       <c r="D92" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F92" s="2">
-        <v>3435711</v>
+        <v>1842843</v>
       </c>
       <c r="G92" s="2">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="H92" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>70</v>
+        <v>249</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>71</v>
+        <v>250</v>
       </c>
       <c r="D93" s="2">
         <v>2</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F93" s="2">
-        <v>4392170</v>
+        <v>2571190</v>
       </c>
       <c r="G93" s="2">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="H93" s="2">
         <v>0</v>
@@ -4230,48 +4219,48 @@
         <v>21</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>134</v>
+        <v>42</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>135</v>
+        <v>43</v>
       </c>
       <c r="D94" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F94" s="2">
-        <v>1758752</v>
+        <v>3218866</v>
       </c>
       <c r="G94" s="2">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="H94" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>173</v>
+        <v>406</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>174</v>
+        <v>407</v>
       </c>
       <c r="D95" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F95" s="2">
-        <v>1740446</v>
+        <v>5930518</v>
       </c>
       <c r="G95" s="2">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="H95" s="2">
         <v>0</v>
@@ -4282,10 +4271,10 @@
         <v>21</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>408</v>
+        <v>191</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>409</v>
+        <v>190</v>
       </c>
       <c r="D96" s="2">
         <v>4</v>
@@ -4294,10 +4283,10 @@
         <v>13</v>
       </c>
       <c r="F96" s="2">
-        <v>7208507</v>
+        <v>3369135</v>
       </c>
       <c r="G96" s="2">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="H96" s="2">
         <v>0</v>
@@ -4308,10 +4297,10 @@
         <v>21</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>356</v>
+        <v>134</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>357</v>
+        <v>135</v>
       </c>
       <c r="D97" s="2">
         <v>4</v>
@@ -4320,62 +4309,62 @@
         <v>13</v>
       </c>
       <c r="F97" s="2">
-        <v>2923606</v>
+        <v>1758752</v>
       </c>
       <c r="G97" s="2">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="H97" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>338</v>
+        <v>393</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>339</v>
+        <v>394</v>
       </c>
       <c r="D98" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F98" s="2">
-        <v>1086552</v>
+        <v>2571190</v>
       </c>
       <c r="G98" s="2">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="H98" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A99" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>187</v>
+        <v>342</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>188</v>
+        <v>343</v>
       </c>
       <c r="D99" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F99" s="2">
-        <v>1494406</v>
+        <v>2137934</v>
       </c>
       <c r="G99" s="2">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="H99" s="2">
         <v>0</v>
@@ -4386,10 +4375,10 @@
         <v>21</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>128</v>
+        <v>408</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>129</v>
+        <v>409</v>
       </c>
       <c r="D100" s="2">
         <v>4</v>
@@ -4398,10 +4387,10 @@
         <v>13</v>
       </c>
       <c r="F100" s="2">
-        <v>1112262</v>
+        <v>7208507</v>
       </c>
       <c r="G100" s="2">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="H100" s="2">
         <v>0</v>
@@ -4412,10 +4401,10 @@
         <v>21</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>328</v>
+        <v>356</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>329</v>
+        <v>357</v>
       </c>
       <c r="D101" s="2">
         <v>4</v>
@@ -4424,42 +4413,42 @@
         <v>13</v>
       </c>
       <c r="F101" s="2">
-        <v>1112262</v>
+        <v>2923606</v>
       </c>
       <c r="G101" s="2">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="H101" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>251</v>
+        <v>121</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>252</v>
+        <v>120</v>
       </c>
       <c r="D102" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F102" s="2">
-        <v>2571190</v>
+        <v>5293627</v>
       </c>
       <c r="G102" s="2">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="H102" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
         <v>14</v>
       </c>
@@ -4485,53 +4474,53 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>336</v>
+        <v>82</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>337</v>
+        <v>83</v>
       </c>
       <c r="D104" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F104" s="2">
-        <v>2903204</v>
+        <v>3013005</v>
       </c>
       <c r="G104" s="2">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="H104" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A105" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>206</v>
+        <v>293</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>207</v>
+        <v>294</v>
       </c>
       <c r="D105" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F105" s="2">
-        <v>2903204</v>
+        <v>3013005</v>
       </c>
       <c r="G105" s="2">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="H105" s="2">
         <v>0</v>
@@ -4542,10 +4531,10 @@
         <v>21</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>340</v>
+        <v>128</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>341</v>
+        <v>129</v>
       </c>
       <c r="D106" s="2">
         <v>4</v>
@@ -4554,65 +4543,65 @@
         <v>13</v>
       </c>
       <c r="F106" s="2">
-        <v>4321939</v>
+        <v>1112262</v>
       </c>
       <c r="G106" s="2">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="H106" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A107" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>236</v>
+        <v>418</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>237</v>
+        <v>419</v>
       </c>
       <c r="D107" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F107" s="2">
-        <v>6933704</v>
+        <v>5213213</v>
       </c>
       <c r="G107" s="2">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="H107" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>283</v>
+        <v>208</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>284</v>
+        <v>209</v>
       </c>
       <c r="D108" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F108" s="2">
-        <v>1267061</v>
+        <v>2238227</v>
       </c>
       <c r="G108" s="2">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="H108" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.35">
@@ -4620,10 +4609,10 @@
         <v>21</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>144</v>
+        <v>328</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>145</v>
+        <v>329</v>
       </c>
       <c r="D109" s="2">
         <v>4</v>
@@ -4632,36 +4621,36 @@
         <v>13</v>
       </c>
       <c r="F109" s="2">
-        <v>3261519</v>
+        <v>1112262</v>
       </c>
       <c r="G109" s="2">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H109" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>234</v>
+        <v>185</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>235</v>
+        <v>186</v>
       </c>
       <c r="D110" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F110" s="2">
-        <v>3258742</v>
+        <v>2137934</v>
       </c>
       <c r="G110" s="2">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="H110" s="2">
         <v>0</v>
@@ -4672,10 +4661,10 @@
         <v>21</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>124</v>
+        <v>340</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>125</v>
+        <v>341</v>
       </c>
       <c r="D111" s="2">
         <v>4</v>
@@ -4684,232 +4673,232 @@
         <v>13</v>
       </c>
       <c r="F111" s="2">
-        <v>2148154</v>
+        <v>4321939</v>
       </c>
       <c r="G111" s="2">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H111" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>287</v>
+        <v>144</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>288</v>
+        <v>145</v>
       </c>
       <c r="D112" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F112" s="2">
-        <v>1121323</v>
+        <v>3261519</v>
       </c>
       <c r="G112" s="2">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H112" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A113" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>249</v>
+        <v>316</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>250</v>
+        <v>317</v>
       </c>
       <c r="D113" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F113" s="2">
-        <v>2571190</v>
+        <v>1093367</v>
       </c>
       <c r="G113" s="2">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="H113" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>354</v>
+        <v>11</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>355</v>
+        <v>12</v>
       </c>
       <c r="D114" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F114" s="2">
-        <v>7248701</v>
+        <v>2107934</v>
       </c>
       <c r="G114" s="2">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="H114" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A115" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>42</v>
+        <v>124</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>43</v>
+        <v>125</v>
       </c>
       <c r="D115" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F115" s="2">
-        <v>3218866</v>
+        <v>2148154</v>
       </c>
       <c r="G115" s="2">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H115" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>364</v>
+        <v>76</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>365</v>
+        <v>77</v>
       </c>
       <c r="D116" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F116" s="2">
-        <v>2757489</v>
+        <v>5715408</v>
       </c>
       <c r="G116" s="2">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H116" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A117" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>360</v>
+        <v>216</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>361</v>
+        <v>217</v>
       </c>
       <c r="D117" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F117" s="2">
-        <v>3435711</v>
+        <v>3013005</v>
       </c>
       <c r="G117" s="2">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="H117" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>320</v>
+        <v>154</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>321</v>
+        <v>155</v>
       </c>
       <c r="D118" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F118" s="2">
-        <v>1086552</v>
+        <v>1767743</v>
       </c>
       <c r="G118" s="2">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H118" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A119" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>140</v>
+        <v>414</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>141</v>
+        <v>415</v>
       </c>
       <c r="D119" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F119" s="2">
-        <v>1090407</v>
+        <v>5856415</v>
       </c>
       <c r="G119" s="2">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="H119" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>316</v>
+        <v>381</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>317</v>
+        <v>382</v>
       </c>
       <c r="D120" s="2">
         <v>3</v>
@@ -4918,128 +4907,128 @@
         <v>13</v>
       </c>
       <c r="F120" s="2">
-        <v>1093367</v>
+        <v>5475421</v>
       </c>
       <c r="G120" s="2">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="H120" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A121" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D121" s="2">
         <v>4</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F121" s="2">
-        <v>1093367</v>
+        <v>1740446</v>
       </c>
       <c r="G121" s="2">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="H121" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A122" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>175</v>
+        <v>338</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>176</v>
+        <v>339</v>
       </c>
       <c r="D122" s="2">
         <v>4</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F122" s="2">
-        <v>2311022</v>
+        <v>1086552</v>
       </c>
       <c r="G122" s="2">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="H122" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A123" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>76</v>
+        <v>364</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>77</v>
+        <v>365</v>
       </c>
       <c r="D123" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F123" s="2">
-        <v>5715408</v>
+        <v>2757489</v>
       </c>
       <c r="G123" s="2">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="H123" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>154</v>
+        <v>320</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>155</v>
+        <v>321</v>
       </c>
       <c r="D124" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F124" s="2">
-        <v>1767743</v>
+        <v>1086552</v>
       </c>
       <c r="G124" s="2">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H124" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A125" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>169</v>
+        <v>140</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>170</v>
+        <v>141</v>
       </c>
       <c r="D125" s="2">
         <v>4</v>
@@ -5048,102 +5037,102 @@
         <v>13</v>
       </c>
       <c r="F125" s="2">
-        <v>2571190</v>
+        <v>1090407</v>
       </c>
       <c r="G125" s="2">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H125" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A126" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="D126" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F126" s="2">
-        <v>3258742</v>
+        <v>3048102</v>
       </c>
       <c r="G126" s="2">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="H126" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A127" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>293</v>
+        <v>336</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>294</v>
+        <v>337</v>
       </c>
       <c r="D127" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F127" s="2">
-        <v>3013005</v>
+        <v>2903204</v>
       </c>
       <c r="G127" s="2">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="H127" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A128" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>406</v>
+        <v>177</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>407</v>
+        <v>178</v>
       </c>
       <c r="D128" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F128" s="2">
-        <v>5930518</v>
+        <v>1093367</v>
       </c>
       <c r="G128" s="2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H128" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A129" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="D129" s="2">
         <v>4</v>
@@ -5152,10 +5141,10 @@
         <v>13</v>
       </c>
       <c r="F129" s="2">
-        <v>2107934</v>
+        <v>2903204</v>
       </c>
       <c r="G129" s="2">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="H129" s="2">
         <v>0</v>
@@ -5187,67 +5176,67 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A131" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>414</v>
+        <v>175</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>415</v>
+        <v>176</v>
       </c>
       <c r="D131" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F131" s="2">
-        <v>5856415</v>
+        <v>2311022</v>
       </c>
       <c r="G131" s="2">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="H131" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A132" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>194</v>
+        <v>387</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>195</v>
+        <v>388</v>
       </c>
       <c r="D132" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F132" s="2">
-        <v>1210302</v>
+        <v>1235319</v>
       </c>
       <c r="G132" s="2">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="H132" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A133" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D133" s="2">
         <v>4</v>
@@ -5256,10 +5245,10 @@
         <v>13</v>
       </c>
       <c r="F133" s="2">
-        <v>1086552</v>
+        <v>2571190</v>
       </c>
       <c r="G133" s="2">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H133" s="2">
         <v>0</v>
@@ -5291,67 +5280,67 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A135" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>410</v>
+        <v>236</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>411</v>
+        <v>237</v>
       </c>
       <c r="D135" s="2">
         <v>4</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F135" s="2">
-        <v>1214802</v>
+        <v>6933704</v>
       </c>
       <c r="G135" s="2">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="H135" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A136" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>208</v>
+        <v>283</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>209</v>
+        <v>284</v>
       </c>
       <c r="D136" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F136" s="2">
-        <v>2238227</v>
+        <v>1267061</v>
       </c>
       <c r="G136" s="2">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="H136" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A137" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>295</v>
+        <v>171</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>296</v>
+        <v>172</v>
       </c>
       <c r="D137" s="2">
         <v>4</v>
@@ -5360,24 +5349,24 @@
         <v>13</v>
       </c>
       <c r="F137" s="2">
-        <v>2311022</v>
+        <v>1086552</v>
       </c>
       <c r="G137" s="2">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H137" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A138" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>366</v>
+        <v>189</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>367</v>
+        <v>190</v>
       </c>
       <c r="D138" s="2">
         <v>4</v>
@@ -5386,10 +5375,10 @@
         <v>13</v>
       </c>
       <c r="F138" s="2">
-        <v>2092090</v>
+        <v>3258742</v>
       </c>
       <c r="G138" s="2">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="H138" s="2">
         <v>0</v>
@@ -5447,67 +5436,67 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A141" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>381</v>
+        <v>295</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>382</v>
+        <v>296</v>
       </c>
       <c r="D141" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F141" s="2">
-        <v>5475421</v>
+        <v>2311022</v>
       </c>
       <c r="G141" s="2">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="H141" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A142" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="D142" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F142" s="2">
-        <v>5213213</v>
+        <v>1214802</v>
       </c>
       <c r="G142" s="2">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="H142" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A143" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>289</v>
+        <v>366</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>290</v>
+        <v>367</v>
       </c>
       <c r="D143" s="2">
         <v>4</v>
@@ -5516,50 +5505,50 @@
         <v>13</v>
       </c>
       <c r="F143" s="2">
-        <v>2028216</v>
+        <v>2092090</v>
       </c>
       <c r="G143" s="2">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H143" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A144" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>54</v>
+        <v>241</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>55</v>
+        <v>242</v>
       </c>
       <c r="D144" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F144" s="2">
-        <v>6112322</v>
+        <v>4576344</v>
       </c>
       <c r="G144" s="2">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H144" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="145" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A145" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>318</v>
+        <v>354</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>319</v>
+        <v>355</v>
       </c>
       <c r="D145" s="2">
         <v>4</v>
@@ -5568,13 +5557,13 @@
         <v>13</v>
       </c>
       <c r="F145" s="2">
-        <v>2238227</v>
+        <v>7248701</v>
       </c>
       <c r="G145" s="2">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="H145" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.35">
@@ -5603,33 +5592,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A147" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>202</v>
+        <v>289</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>203</v>
+        <v>290</v>
       </c>
       <c r="D147" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F147" s="2">
-        <v>3048102</v>
+        <v>2028216</v>
       </c>
       <c r="G147" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H147" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A148" s="2" t="s">
         <v>27</v>
       </c>
@@ -5655,7 +5644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A149" s="2" t="s">
         <v>14</v>
       </c>
@@ -5681,15 +5670,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A150" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>387</v>
+        <v>368</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>388</v>
+        <v>369</v>
       </c>
       <c r="D150" s="2">
         <v>3</v>
@@ -5698,16 +5687,16 @@
         <v>13</v>
       </c>
       <c r="F150" s="2">
-        <v>1235319</v>
+        <v>1707115</v>
       </c>
       <c r="G150" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H150" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A151" s="2" t="s">
         <v>14</v>
       </c>
@@ -5733,7 +5722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A152" s="2" t="s">
         <v>14</v>
       </c>
@@ -5759,41 +5748,41 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A153" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>241</v>
+        <v>194</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>242</v>
+        <v>195</v>
       </c>
       <c r="D153" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E153" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F153" s="2">
-        <v>4576344</v>
+        <v>1210302</v>
       </c>
       <c r="G153" s="2">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="H153" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A154" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>240</v>
+        <v>54</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>239</v>
+        <v>55</v>
       </c>
       <c r="D154" s="2">
         <v>4</v>
@@ -5802,24 +5791,24 @@
         <v>13</v>
       </c>
       <c r="F154" s="2">
-        <v>5318224</v>
+        <v>6112322</v>
       </c>
       <c r="G154" s="2">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H154" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="155" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A155" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>348</v>
+        <v>240</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>349</v>
+        <v>239</v>
       </c>
       <c r="D155" s="2">
         <v>4</v>
@@ -5828,24 +5817,24 @@
         <v>13</v>
       </c>
       <c r="F155" s="2">
-        <v>2832797</v>
+        <v>5318224</v>
       </c>
       <c r="G155" s="2">
         <v>20</v>
       </c>
       <c r="H155" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="156" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A156" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="D156" s="2">
         <v>4</v>
@@ -5854,16 +5843,16 @@
         <v>13</v>
       </c>
       <c r="F156" s="2">
-        <v>3371830</v>
+        <v>2832797</v>
       </c>
       <c r="G156" s="2">
         <v>20</v>
       </c>
       <c r="H156" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="157" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A157" s="2" t="s">
         <v>27</v>
       </c>
@@ -5889,7 +5878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A158" s="2" t="s">
         <v>27</v>
       </c>
@@ -5915,15 +5904,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A159" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>92</v>
+        <v>360</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>93</v>
+        <v>361</v>
       </c>
       <c r="D159" s="2">
         <v>4</v>
@@ -5932,16 +5921,16 @@
         <v>13</v>
       </c>
       <c r="F159" s="2">
-        <v>7248701</v>
+        <v>3435711</v>
       </c>
       <c r="G159" s="2">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="H159" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A160" s="2" t="s">
         <v>17</v>
       </c>
@@ -5967,15 +5956,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A161" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>279</v>
+        <v>344</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>280</v>
+        <v>345</v>
       </c>
       <c r="D161" s="2">
         <v>4</v>
@@ -5984,24 +5973,24 @@
         <v>13</v>
       </c>
       <c r="F161" s="2">
-        <v>1457877</v>
+        <v>3371830</v>
       </c>
       <c r="G161" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H161" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A162" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>156</v>
+        <v>279</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>157</v>
+        <v>280</v>
       </c>
       <c r="D162" s="2">
         <v>4</v>
@@ -6010,7 +5999,7 @@
         <v>13</v>
       </c>
       <c r="F162" s="2">
-        <v>5018255</v>
+        <v>1457877</v>
       </c>
       <c r="G162" s="2">
         <v>19</v>
@@ -6019,15 +6008,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A163" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>224</v>
+        <v>156</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>225</v>
+        <v>157</v>
       </c>
       <c r="D163" s="2">
         <v>4</v>
@@ -6036,7 +6025,7 @@
         <v>13</v>
       </c>
       <c r="F163" s="2">
-        <v>5299061</v>
+        <v>5018255</v>
       </c>
       <c r="G163" s="2">
         <v>19</v>
@@ -6045,7 +6034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A164" s="2" t="s">
         <v>27</v>
       </c>
@@ -6071,7 +6060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A165" s="2" t="s">
         <v>27</v>
       </c>
@@ -6097,7 +6086,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A166" s="2" t="s">
         <v>27</v>
       </c>
@@ -6123,7 +6112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A167" s="2" t="s">
         <v>27</v>
       </c>
@@ -6149,24 +6138,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A168" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>395</v>
+        <v>251</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>396</v>
+        <v>252</v>
       </c>
       <c r="D168" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F168" s="2">
-        <v>4205238</v>
+        <v>3074554</v>
       </c>
       <c r="G168" s="2">
         <v>18</v>
@@ -6175,24 +6164,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A169" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>251</v>
+        <v>395</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>252</v>
+        <v>396</v>
       </c>
       <c r="D169" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F169" s="2">
-        <v>3074554</v>
+        <v>4205238</v>
       </c>
       <c r="G169" s="2">
         <v>18</v>
@@ -6201,33 +6190,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A170" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>368</v>
+        <v>224</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>369</v>
+        <v>225</v>
       </c>
       <c r="D170" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E170" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F170" s="2">
-        <v>1707115</v>
+        <v>5299061</v>
       </c>
       <c r="G170" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H170" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A171" s="2" t="s">
         <v>24</v>
       </c>
@@ -6253,7 +6242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A172" s="2" t="s">
         <v>24</v>
       </c>
@@ -6279,7 +6268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A173" s="2" t="s">
         <v>24</v>
       </c>
@@ -6305,7 +6294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A174" s="2" t="s">
         <v>24</v>
       </c>
@@ -6331,7 +6320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A175" s="2" t="s">
         <v>24</v>
       </c>
@@ -6357,7 +6346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A176" s="2" t="s">
         <v>24</v>
       </c>
@@ -6383,7 +6372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A177" s="2" t="s">
         <v>27</v>
       </c>
@@ -6409,7 +6398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A178" s="2" t="s">
         <v>17</v>
       </c>
@@ -6435,7 +6424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A179" s="2" t="s">
         <v>24</v>
       </c>
@@ -6461,7 +6450,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A180" s="2" t="s">
         <v>24</v>
       </c>
@@ -6487,7 +6476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A181" s="2" t="s">
         <v>27</v>
       </c>
@@ -6513,59 +6502,59 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A182" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>36</v>
+        <v>350</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>37</v>
+        <v>351</v>
       </c>
       <c r="D182" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E182" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F182" s="2">
-        <v>1463803</v>
+        <v>2832797</v>
       </c>
       <c r="G182" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H182" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A183" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>34</v>
+        <v>198</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>35</v>
+        <v>199</v>
       </c>
       <c r="D183" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F183" s="2">
-        <v>2719999</v>
+        <v>1666337</v>
       </c>
       <c r="G183" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H183" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A184" s="2" t="s">
         <v>14</v>
       </c>
@@ -6591,7 +6580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A185" s="2" t="s">
         <v>14</v>
       </c>
@@ -6617,7 +6606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A186" s="2" t="s">
         <v>24</v>
       </c>
@@ -6643,7 +6632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A187" s="2" t="s">
         <v>17</v>
       </c>
@@ -6669,79 +6658,79 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A188" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>350</v>
+        <v>152</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>351</v>
+        <v>153</v>
       </c>
       <c r="D188" s="2">
         <v>2</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F188" s="2">
-        <v>2832797</v>
+        <v>2355205</v>
       </c>
       <c r="G188" s="2">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H188" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A189" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="D189" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E189" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F189" s="2">
-        <v>3074554</v>
+        <v>1583231</v>
       </c>
       <c r="G189" s="2">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H189" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="190" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A190" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D190" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F190" s="2">
-        <v>1463503</v>
+        <v>1463803</v>
       </c>
       <c r="G190" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H190" s="2">
         <v>0</v>
@@ -6799,7 +6788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A193" s="2" t="s">
         <v>24</v>
       </c>
@@ -6825,59 +6814,59 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A194" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>198</v>
+        <v>72</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>199</v>
+        <v>73</v>
       </c>
       <c r="D194" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E194" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F194" s="2">
-        <v>1666337</v>
+        <v>3074554</v>
       </c>
       <c r="G194" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H194" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A195" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>148</v>
+        <v>214</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>149</v>
+        <v>215</v>
       </c>
       <c r="D195" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F195" s="2">
-        <v>9931948</v>
+        <v>2107934</v>
       </c>
       <c r="G195" s="2">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="H195" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A196" s="2" t="s">
         <v>17</v>
       </c>
@@ -6903,33 +6892,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A197" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>11</v>
+        <v>318</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>12</v>
+        <v>319</v>
       </c>
       <c r="D197" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E197" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F197" s="2">
-        <v>2107934</v>
+        <v>2238227</v>
       </c>
       <c r="G197" s="2">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="H197" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A198" s="2" t="s">
         <v>17</v>
       </c>
@@ -6955,24 +6944,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A199" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>152</v>
+        <v>412</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>153</v>
+        <v>413</v>
       </c>
       <c r="D199" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F199" s="2">
-        <v>2355205</v>
+        <v>2002083</v>
       </c>
       <c r="G199" s="2">
         <v>11</v>
@@ -6981,15 +6970,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A200" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>412</v>
+        <v>99</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>413</v>
+        <v>100</v>
       </c>
       <c r="D200" s="2">
         <v>3</v>
@@ -6998,232 +6987,232 @@
         <v>13</v>
       </c>
       <c r="F200" s="2">
-        <v>2002083</v>
+        <v>3979315</v>
       </c>
       <c r="G200" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H200" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A201" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>105</v>
+        <v>165</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>106</v>
+        <v>166</v>
       </c>
       <c r="D201" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E201" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F201" s="2">
-        <v>2433502</v>
+        <v>4419464</v>
       </c>
       <c r="G201" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H201" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A202" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>216</v>
+        <v>92</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>217</v>
+        <v>93</v>
       </c>
       <c r="D202" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E202" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F202" s="2">
-        <v>3013005</v>
+        <v>7248701</v>
       </c>
       <c r="G202" s="2">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="H202" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A203" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="D203" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E203" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F203" s="2">
-        <v>1583231</v>
+        <v>3074554</v>
       </c>
       <c r="G203" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H203" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="204" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A204" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>136</v>
+        <v>34</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>137</v>
+        <v>35</v>
       </c>
       <c r="D204" s="2">
         <v>4</v>
       </c>
       <c r="E204" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F204" s="2">
-        <v>2002083</v>
+        <v>2719999</v>
       </c>
       <c r="G204" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H204" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A205" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="D205" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E205" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F205" s="2">
-        <v>1608770</v>
+        <v>3633158</v>
       </c>
       <c r="G205" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H205" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A206" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>266</v>
+        <v>291</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>267</v>
+        <v>292</v>
       </c>
       <c r="D206" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E206" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F206" s="2">
-        <v>3258742</v>
+        <v>1009202</v>
       </c>
       <c r="G206" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H206" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A207" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>424</v>
+        <v>375</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>425</v>
+        <v>376</v>
       </c>
       <c r="D207" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E207" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F207" s="2">
-        <v>5997408</v>
+        <v>1410757</v>
       </c>
       <c r="G207" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H207" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A208" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>238</v>
+        <v>32</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>239</v>
+        <v>33</v>
       </c>
       <c r="D208" s="2">
         <v>4</v>
       </c>
       <c r="E208" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F208" s="2">
-        <v>2355205</v>
+        <v>1463503</v>
       </c>
       <c r="G208" s="2">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H208" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A209" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>268</v>
+        <v>18</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>269</v>
+        <v>16</v>
       </c>
       <c r="D209" s="2">
         <v>2</v>
@@ -7232,50 +7221,50 @@
         <v>10</v>
       </c>
       <c r="F209" s="2">
-        <v>3633158</v>
+        <v>1098471</v>
       </c>
       <c r="G209" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H209" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A210" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>291</v>
+        <v>350</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>292</v>
+        <v>351</v>
       </c>
       <c r="D210" s="2">
         <v>2</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F210" s="2">
-        <v>1009202</v>
+        <v>2832797</v>
       </c>
       <c r="G210" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H210" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A211" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>375</v>
+        <v>243</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>376</v>
+        <v>244</v>
       </c>
       <c r="D211" s="2">
         <v>2</v>
@@ -7287,151 +7276,151 @@
         <v>1410757</v>
       </c>
       <c r="G211" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H211" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A212" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>80</v>
+        <v>196</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>81</v>
+        <v>197</v>
       </c>
       <c r="D212" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E212" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F212" s="2">
-        <v>1498302</v>
+        <v>2190106</v>
       </c>
       <c r="G212" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H212" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A213" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>404</v>
+        <v>281</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>405</v>
+        <v>282</v>
       </c>
       <c r="D213" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E213" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F213" s="2">
-        <v>1410757</v>
+        <v>1009202</v>
       </c>
       <c r="G213" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H213" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A214" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="D214" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E214" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F214" s="2">
-        <v>3979315</v>
+        <v>2433502</v>
       </c>
       <c r="G214" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H214" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A215" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>165</v>
+        <v>136</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>166</v>
+        <v>137</v>
       </c>
       <c r="D215" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E215" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F215" s="2">
-        <v>4419464</v>
+        <v>2002083</v>
       </c>
       <c r="G215" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H215" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A216" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>18</v>
+        <v>346</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>16</v>
+        <v>347</v>
       </c>
       <c r="D216" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E216" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F216" s="2">
-        <v>1098471</v>
+        <v>2446060</v>
       </c>
       <c r="G216" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H216" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A217" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>196</v>
+        <v>428</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>197</v>
+        <v>429</v>
       </c>
       <c r="D217" s="2">
         <v>3</v>
@@ -7440,250 +7429,250 @@
         <v>10</v>
       </c>
       <c r="F217" s="2">
-        <v>2190106</v>
+        <v>1892200</v>
       </c>
       <c r="G217" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H217" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A218" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>350</v>
+        <v>245</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>351</v>
+        <v>246</v>
       </c>
       <c r="D218" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E218" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F218" s="2">
-        <v>2832797</v>
+        <v>2446060</v>
       </c>
       <c r="G218" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H218" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A219" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="D219" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E219" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F219" s="2">
-        <v>1410757</v>
+        <v>1608770</v>
       </c>
       <c r="G219" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H219" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A220" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>281</v>
+        <v>310</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>282</v>
+        <v>311</v>
       </c>
       <c r="D220" s="2">
         <v>3</v>
       </c>
       <c r="E220" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F220" s="2">
-        <v>1009202</v>
+        <v>3633158</v>
       </c>
       <c r="G220" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H220" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A221" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>346</v>
+        <v>255</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>347</v>
+        <v>256</v>
       </c>
       <c r="D221" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E221" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F221" s="2">
-        <v>2446060</v>
+        <v>1608770</v>
       </c>
       <c r="G221" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H221" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A222" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>68</v>
+        <v>238</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>69</v>
+        <v>239</v>
       </c>
       <c r="D222" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E222" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F222" s="2">
-        <v>3074554</v>
+        <v>2355205</v>
       </c>
       <c r="G222" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H222" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A223" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>428</v>
+        <v>266</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>429</v>
+        <v>267</v>
       </c>
       <c r="D223" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E223" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F223" s="2">
-        <v>1892200</v>
+        <v>3258742</v>
       </c>
       <c r="G223" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H223" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A224" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>245</v>
+        <v>424</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>246</v>
+        <v>425</v>
       </c>
       <c r="D224" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E224" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F224" s="2">
-        <v>2446060</v>
+        <v>5997408</v>
       </c>
       <c r="G224" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H224" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A225" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>247</v>
+        <v>80</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>248</v>
+        <v>81</v>
       </c>
       <c r="D225" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E225" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F225" s="2">
-        <v>1608770</v>
+        <v>1498302</v>
       </c>
       <c r="G225" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H225" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A226" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>310</v>
+        <v>404</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>311</v>
+        <v>405</v>
       </c>
       <c r="D226" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E226" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F226" s="2">
-        <v>3633158</v>
+        <v>1410757</v>
       </c>
       <c r="G226" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H226" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A227" s="2" t="s">
         <v>7</v>
       </c>
